--- a/03_Cluster_groups/Proteome/02_Design_Contrasts/c_data/design_contrasts_all_inputs.xlsx
+++ b/03_Cluster_groups/Proteome/02_Design_Contrasts/c_data/design_contrasts_all_inputs.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="205">
   <si>
     <t>sheet</t>
   </si>
@@ -234,31 +234,31 @@
     <t>03_Cluster_groups/Proteome/02_Design_Contrasts/T1/c_data/design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>facacc6ac3cb7c33cd569ec7b4ddc2ff</t>
+    <t>5ab2f5d0b8715f9eee7d87d89dfce434</t>
   </si>
   <si>
     <t>03_Cluster_groups/Proteome/02_Design_Contrasts/T2/c_data/design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>6f5e69705d142791ffd42d50cf866146</t>
+    <t>2c74bebe84edb69abb815389df117f90</t>
   </si>
   <si>
     <t>03_Cluster_groups/Proteome/02_Design_Contrasts/T3/c_data/design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>0e8f45338c7ef4b3961090117e4584e6</t>
+    <t>83a130c3f5879a8ea819f48d9abf7a4f</t>
   </si>
   <si>
     <t>03_Cluster_groups/Proteome/02_Design_Contrasts/training/c_data/design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>7c17ea4115812ae478534c135348d35e</t>
+    <t>3c54d189dc3fdd622a71675ea64d9b2c</t>
   </si>
   <si>
     <t>03_Cluster_groups/Proteome/02_Design_Contrasts/acute/c_data/design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>05e87bbcd2d8649d382e6d4b9ec5e32b</t>
+    <t>58284aa005b707d71c5b7190dc2f9ff3</t>
   </si>
   <si>
     <t>BiocGenerics</t>
@@ -628,6 +628,12 @@
   </si>
   <si>
     <t>2.0.1</t>
+  </si>
+  <si>
+    <t>yaml</t>
+  </si>
+  <si>
+    <t>2.3.12</t>
   </si>
 </sst>
 </file>
@@ -2147,7 +2153,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -2832,6 +2838,17 @@
         <v>171</v>
       </c>
     </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>203</v>
+      </c>
+      <c r="B63" t="s">
+        <v>204</v>
+      </c>
+      <c r="C63" t="s">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
